--- a/project_5/software/f1_sft_1/XR自定命令词播报词协议列表-人形版本V1.xlsx
+++ b/project_5/software/f1_sft_1/XR自定命令词播报词协议列表-人形版本V1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\11_pro_develop\ezProject_2026\reference\XRVoice语音模块\04.Pico-16版本使用说明\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\11_pro_develop\ezProject_2026\project_5\software\f1_sft_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F96C38-6054-4A45-999A-AF6D66D6D45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93683DB2-DB62-41B7-AAD0-2A6C81D6E826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="197">
   <si>
     <t>语义标签</t>
   </si>
@@ -248,111 +248,39 @@
     <t>FF 00 04 00 FF</t>
   </si>
   <si>
-    <t>打个招呼</t>
-  </si>
-  <si>
-    <t>你好+很高兴见到你</t>
-  </si>
-  <si>
     <t>FF 00 05 00 FF</t>
   </si>
   <si>
-    <t>再次打个招呼</t>
-  </si>
-  <si>
-    <t>今天心情不错哟</t>
-  </si>
-  <si>
     <t>FF 00 06 00 FF</t>
   </si>
   <si>
-    <t>右直拳</t>
-  </si>
-  <si>
-    <t>看招+右直拳</t>
-  </si>
-  <si>
     <t>FF 00 07 00 FF</t>
   </si>
   <si>
-    <t>右勾拳</t>
-  </si>
-  <si>
-    <t>看招+右勾拳</t>
-  </si>
-  <si>
     <t>FF 00 08 00 FF</t>
   </si>
   <si>
-    <t>右上勾拳</t>
-  </si>
-  <si>
-    <t>右手上勾拳</t>
-  </si>
-  <si>
     <t>FF 00 09 00 FF</t>
   </si>
   <si>
-    <t>左直拳</t>
-  </si>
-  <si>
-    <t>看招+左直拳</t>
-  </si>
-  <si>
     <t>FF 00 0A 00 FF</t>
   </si>
   <si>
-    <t>左勾拳</t>
-  </si>
-  <si>
-    <t>看招+左勾拳</t>
-  </si>
-  <si>
     <t>FF 00 0B 00 FF</t>
   </si>
   <si>
-    <t>左上勾拳</t>
-  </si>
-  <si>
-    <t>左手上勾拳</t>
-  </si>
-  <si>
     <t>FF 00 0C 00 FF</t>
   </si>
   <si>
-    <t>挥右手</t>
-  </si>
-  <si>
-    <t>向右挥手</t>
-  </si>
-  <si>
     <t>FF 00 0D 00 FF</t>
   </si>
   <si>
-    <t>挥左手</t>
-  </si>
-  <si>
-    <t>向左挥手</t>
-  </si>
-  <si>
     <t>FF 00 0E 00 FF</t>
   </si>
   <si>
-    <t>右转</t>
-  </si>
-  <si>
-    <t>转身+看右边</t>
-  </si>
-  <si>
     <t>FF 00 0F 00 FF</t>
   </si>
   <si>
-    <t>左转</t>
-  </si>
-  <si>
-    <t>转身+看左边</t>
-  </si>
-  <si>
     <t>FF 00 10 00 FF</t>
   </si>
   <si>
@@ -579,9 +507,6 @@
   </si>
   <si>
     <t>FF 00 29 00 FF</t>
-  </si>
-  <si>
-    <t>骑马舞</t>
   </si>
   <si>
     <t>江南范儿+走起</t>
@@ -710,6 +635,74 @@
     <t>2、如果某个命令词的识别不够灵敏，可在页面上更改该命令词的置信度阈值提高其识别灵敏度（非自动优化模式）；也可以增加同一语义的命令词以提高其识别泛化性</t>
   </si>
   <si>
+    <t>前方有障碍物</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>左转</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>右转</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>直行</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测到摔倒</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间一点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间两点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间三点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间四点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间五点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间六点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间七点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间八点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间九点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间十点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间十一点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在时间十二点整</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>自定义一</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -730,23 +723,51 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>前方有障碍物</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>左转</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>右转</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>直行</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测到摔倒</t>
+    <t>自定义六</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义七</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义八</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义九</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义十</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义十一</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义十二</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义十三</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义十四</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义十五</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义十六</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义十七</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1003,11 +1024,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1555,14 +1576,14 @@
       <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>188</v>
+      <c r="B12" s="23" t="s">
+        <v>180</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>193</v>
+      <c r="D12" s="23" t="s">
+        <v>163</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>9</v>
@@ -1578,14 +1599,14 @@
       <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>189</v>
+      <c r="B13" s="23" t="s">
+        <v>181</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>194</v>
+      <c r="D13" s="23" t="s">
+        <v>164</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>9</v>
@@ -1601,14 +1622,14 @@
       <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>190</v>
+      <c r="B14" s="23" t="s">
+        <v>182</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>195</v>
+      <c r="D14" s="23" t="s">
+        <v>165</v>
       </c>
       <c r="E14" s="19" t="s">
         <v>9</v>
@@ -1624,14 +1645,14 @@
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="24" t="s">
-        <v>191</v>
+      <c r="B15" s="23" t="s">
+        <v>183</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>196</v>
+      <c r="D15" s="23" t="s">
+        <v>166</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>9</v>
@@ -1647,14 +1668,14 @@
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>192</v>
+      <c r="B16" s="23" t="s">
+        <v>184</v>
       </c>
       <c r="C16" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>197</v>
+      <c r="D16" s="23" t="s">
+        <v>167</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>9</v>
@@ -1670,276 +1691,276 @@
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>41</v>
-      </c>
       <c r="G17" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>42</v>
+      <c r="B18" s="23" t="s">
+        <v>186</v>
       </c>
       <c r="C18" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>43</v>
+      <c r="D18" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>45</v>
+      <c r="B19" s="23" t="s">
+        <v>187</v>
       </c>
       <c r="C19" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>46</v>
+      <c r="D19" s="23" t="s">
+        <v>170</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="21" t="s">
-        <v>48</v>
+      <c r="B20" s="23" t="s">
+        <v>188</v>
       </c>
       <c r="C20" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D20" s="21" t="s">
-        <v>49</v>
+      <c r="D20" s="23" t="s">
+        <v>171</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="21" t="s">
-        <v>51</v>
+      <c r="B21" s="23" t="s">
+        <v>189</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>52</v>
+      <c r="D21" s="23" t="s">
+        <v>172</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>54</v>
+      <c r="B22" s="23" t="s">
+        <v>190</v>
       </c>
       <c r="C22" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D22" s="21" t="s">
-        <v>55</v>
+      <c r="D22" s="23" t="s">
+        <v>173</v>
       </c>
       <c r="E22" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>57</v>
+      <c r="B23" s="23" t="s">
+        <v>191</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D23" s="21" t="s">
-        <v>58</v>
+      <c r="D23" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="E23" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>60</v>
+      <c r="B24" s="23" t="s">
+        <v>192</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="21" t="s">
-        <v>61</v>
+      <c r="D24" s="23" t="s">
+        <v>175</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="21" t="s">
-        <v>63</v>
+      <c r="B25" s="23" t="s">
+        <v>193</v>
       </c>
       <c r="C25" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>64</v>
+      <c r="D25" s="23" t="s">
+        <v>176</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="21" t="s">
-        <v>66</v>
+      <c r="B26" s="23" t="s">
+        <v>194</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="21" t="s">
-        <v>67</v>
+      <c r="D26" s="23" t="s">
+        <v>177</v>
       </c>
       <c r="E26" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="21" t="s">
-        <v>69</v>
+      <c r="B27" s="23" t="s">
+        <v>195</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D27" s="21" t="s">
-        <v>70</v>
+      <c r="D27" s="23" t="s">
+        <v>178</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>27</v>
       </c>
-      <c r="B28" s="21" t="s">
-        <v>72</v>
+      <c r="B28" s="23" t="s">
+        <v>196</v>
       </c>
       <c r="C28" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D28" s="21" t="s">
-        <v>73</v>
+      <c r="D28" s="23" t="s">
+        <v>179</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -1947,22 +1968,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="C29" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -1970,22 +1991,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -1993,22 +2014,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C31" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2016,22 +2037,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C32" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2039,22 +2060,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C33" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2062,22 +2083,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C34" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2085,22 +2106,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C35" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2108,22 +2129,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2131,22 +2152,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C37" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="E37" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2154,22 +2175,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="C38" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2177,22 +2198,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="C39" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2200,22 +2221,22 @@
         <v>39</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C40" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2223,22 +2244,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C41" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="E41" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2246,22 +2267,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C42" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="E42" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2269,22 +2290,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C43" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="E43" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2292,22 +2313,22 @@
         <v>43</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="C44" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="E44" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2315,22 +2336,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C45" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E45" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2338,22 +2359,22 @@
         <v>45</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="C46" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2361,22 +2382,22 @@
         <v>46</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="C47" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2384,22 +2405,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="C48" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="E48" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2407,22 +2428,22 @@
         <v>48</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C49" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="E49" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2430,22 +2451,22 @@
         <v>49</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C50" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2453,22 +2474,22 @@
         <v>50</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="C51" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="E51" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2476,22 +2497,22 @@
         <v>51</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="C52" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2499,22 +2520,22 @@
         <v>52</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="C53" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
@@ -2522,22 +2543,22 @@
         <v>53</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="C54" s="22" t="s">
         <v>1</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2571,72 +2592,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23"/>
+      <c r="A1" s="24"/>
     </row>
     <row r="2" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="23"/>
+      <c r="A2" s="24"/>
       <c r="B2" s="2" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="23"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="3" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="23"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="3" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="3" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="3" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="3" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="23"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="3" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="23"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="3" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
+      <c r="A10" s="24"/>
       <c r="B10" s="3" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="23"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="3" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="4" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2652,31 +2673,31 @@
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="7" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="8" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="7" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="8" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2686,25 +2707,25 @@
     <row r="21" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="10" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="11" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="11" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="4" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2713,37 +2734,37 @@
     </row>
     <row r="26" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="69" x14ac:dyDescent="0.25">
       <c r="B30" s="8" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="69" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B32" s="12" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -2753,17 +2774,17 @@
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" s="13" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -2773,7 +2794,7 @@
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -2783,22 +2804,22 @@
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" s="13" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B45" s="6" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B46" s="9" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="2:2" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B47" s="9" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
